--- a/output/2026-09-13_00_Croazia_Varazdinska_Impiantistica_aspirazione_industriale.xlsx
+++ b/output/2026-09-13_00_Croazia_Varazdinska_Impiantistica_aspirazione_industriale.xlsx
@@ -536,10 +536,9 @@
           <t>+385 42 202 146</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Centro Kärcher ufficiale (showroom, assistenza, Kärcher Academy): vendita/assistenza aspiratori industriali professionali a secco/umido e attrezzature per pulizia industriale. Indirizzo: Jalkovečka ulica 76, 42000 Varaždin. Fonti: karcher.com, varazdinske-vijesti.hr, centering.hr.</t>
+          <t>Centro Kärcher ufficiale (showroom, assistenza, Kärcher Academy): vendita/assistenza aspiratori industriali professionali a secco/umido e attrezzature per pulizia industriale. Indirizzo: Jalkovečka ulica 76, 42000 Varaždin. Fonti: karcher.com, varazdinske-vijesti.hr, centering.hr. [DUPLICATO — vedi anche: 2026-09-12_22_Croazia_Varazdinska_Cleaning.xlsx]</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">

--- a/output/2026-09-13_00_Croazia_Varazdinska_Impiantistica_aspirazione_industriale.xlsx
+++ b/output/2026-09-13_00_Croazia_Varazdinska_Impiantistica_aspirazione_industriale.xlsx
@@ -506,7 +506,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (14/09/2026)</t>
         </is>
       </c>
     </row>
